--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_08_Full_112_Cau/Day_08_Ngan_Hang_Phan_02_19_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_08_Full_112_Cau/Day_08_Ngan_Hang_Phan_02_19_Cau.xlsx
@@ -681,7 +681,7 @@
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Phân biệt phần có thể chạy song song với kết luận phụ thuộc chúng.</t>
+          <t>Khi phân rã và kết hợp lại câu hỏi so sánh hai phiên bản chính sách ở hai nguồn riêng: (a) Tạo sub-query lấy điều kiện và hạn chót năm 2026; (b) Tạo sub-query lấy hạn chót năm 2025; (c) Giữ dấu vết nguồn riêng cho từng phiên bản tài liệu; (d) Chỉ đưa ra kết luận so sánh sau khi đã thu thập đủ hạn chót của cả hai năm. Tuyệt đối không dùng trí nhớ của mô hình để suy diễn khi thiếu dữ liệu.</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1349,7 @@
       <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Phân biệt bước xây dựng index offline với bước tìm kiếm khi nhận query.</t>
+          <t>Quy trình triển khai tìm kiếm từ khóa (lexical search BM25) đúng trình tự nhân quả: 1. Xây dựng chỉ mục BM25 từ các token trong kho tài liệu ở pha offline (o3) -&gt; 2. Khi nhận truy vấn, tokenize query theo cùng quy ước chuẩn hóa (o2) -&gt; 3. Chấm điểm truy vấn trên chỉ mục BM25 (o4) -&gt; 4. Sắp xếp điểm giảm dần và giới hạn ở top-k kết quả (o5) -&gt; 5. Trả top-k bản ghi kèm mã định danh và metadata (o1).</t>
         </is>
       </c>
     </row>

--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_08_Full_112_Cau/Day_08_Ngan_Hang_Phan_02_19_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_08_Full_112_Cau/Day_08_Ngan_Hang_Phan_02_19_Cau.xlsx
@@ -624,10 +624,27 @@
       <c r="K3" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Kiểm tra lần lượt Sửa chính tả và Từ đồng nghĩa.
-Phân tích theo nguyên lý thiết kế: Kiểm tra lần lượt Sửa chính tả và Từ đồng nghĩa.</t>
+- [Phân tích ngữ cảnh lựa chọn hạ tầng] (1.0 điểm): Xác định đúng ý định người dùng là chi phí tài chính/hạ tầng (TCO, cloud, hosting) chứ không phải độ phức tạp tính toán.
+- [Thiết kế Query mở rộng chuẩn xác] (1.5 điểm): Đưa ra các query mở rộng hợp lý cho cả sparse và dense, bổ sung từ đồng nghĩa có kiểm soát.
+- [Ranh giới chống bịa đặt ý định] (1.5 điểm): Khẳng định không thêm thắt các tiêu chí so sánh hiệu năng/thuật toán ngoài luồng yêu cầu.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Phân tích ngữ cảnh người dùng:
+Query gốc: `vector db chi phi`.
+Ngữ cảnh quan sát được: Người dùng đang trong quá trình khảo sát và lựa chọn hạ tầng kỹ thuật (Infrastructure Selection).
+Ý định thực sự: Tìm hiểu về tổng chi phí sở hữu (Total Cost of Ownership - TCO) khi triển khai cơ sở dữ liệu vector, bao gồm chi phí bản quyền/dịch vụ đám mây (Cloud hosting / DBaaS pricing), chi phí hạ tầng phần cứng (RAM, CPU, GPU, Storage) và chi phí vận hành bảo trì; KHÔNG PHẢI chi phí tính toán độ phức tạp thuật toán khoảng cách vector (distance computation algorithmic complexity).
+2. Thiết kế mở rộng Query có kiểm soát (Contextual Query Expansion):
+Mở rộng câu hỏi bằng cách bổ sung các từ đồng nghĩa và thuật ngữ hạ tầng liên quan trực tiếp đến ngữ cảnh lựa chọn công nghệ, giữ nguyên ý định mà không bịa thêm tính năng ngoài luồng:
+- **Query mở rộng dạng từ khóa (Lexical / BM25 expansion)**:
+  `vector database chi phí giá dịch vụ cloud hosting pricing TCO hạ tầng server RAM storage`
+- **Query mở rộng dạng ngữ nghĩa đầy đủ (Dense / Semantic expansion)**:
+  `Chi phí bản quyền và hạ tầng triển khai cơ sở dữ liệu vector bao gồm giá cloud managed service và phần cứng vận hành`
+3. Ranh giới an toàn ngăn chặn bịa thêm ý định:
+- Chỉ bổ sung các khía cạnh trực thuộc khái niệm 'chi phí hạ tầng' (hosting, pricing, hardware, cloud).
+- Tuyệt đối không tự ý thêm thắt các tiêu chí so sánh hiệu năng (như latency benchmark, HNSW vs IVF, hay tính năng hybrid search) vì người dùng chưa hề yêu cầu.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Mở rộng truy vấn (Query Expansion) phải tuân thủ nguyên tắc bảo toàn ý định (Intent-Preserving Expansion). Bổ sung từ đồng nghĩa và thuật ngữ ngữ cảnh hạ tầng giúp hệ thống bao phủ các tài liệu báo giá và phân tích TCO, trong khi việc kiểm soát ranh giới nghiêm ngặt ngăn chặn việc làm loãng không gian tìm kiếm bằng các chủ đề không liên quan.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Manning, Raghavan &amp; Schütze: 'Introduction to Information Retrieval' - Chapter 9: Relevance feedback and query expansion</t>
         </is>
       </c>
     </row>
@@ -712,10 +729,29 @@
       <c r="K5" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Kiểm tra lần lượt Ranh giới câu hỏi con và thứ tự phụ thuộc.
-Phân tích theo nguyên lý thiết kế: Kiểm tra lần lượt Ranh giới câu hỏi con và thứ tự phụ thuộc.</t>
+- [Phân rã đúng 2 câu hỏi con có phụ thuộc] (1.5 điểm): Xác định Bước 1 tìm vai trò ở Nguồn A và Bước 2 dùng vai trò đó để tra hạn mức ở Nguồn B.
+- [Quy trình tái hợp nhất câu trả lời] (1.0 điểm): Mô tả rõ bước tổng hợp kết quả kèm trích dẫn Nguồn A và Nguồn B.
+- [Chặn sử dụng trí nhớ mô hình] (1.5 điểm): Nhấn mạnh quy tắc không dùng kiến thức chung của LLM để lấp chỗ trống nếu tài liệu bị khuyết thiếu.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Ranh giới câu hỏi con và thứ tự phụ thuộc (Query Decomposition):
+Câu hỏi gốc: 'Ai phê duyệt việc mua phần mềm và giới hạn số tiền người đó được phê duyệt là bao nhiêu?'.
+Phân tích quan hệ: Đây là bài toán truy xuất đa chặng có phụ thuộc tuần tự (Sequential Multi-hop Dependency): Vế thứ hai (giới hạn số tiền) phụ thuộc trực tiếp vào kết quả của vế thứ nhất (danh tính/vai trò người phê duyệt).
+- **Bước 1 (Truy xuất Danh tính / Vai trò người phê duyệt)**:
+  + Query con 1: `"Vai trò hoặc cấp bậc nào có thẩm quyền phê duyệt mua sắm phần mềm?"`
+  + Nguồn nhắm tới: Nguồn A (Quy trình mua sắm phần mềm / Phân quyền thẩm quyền).
+  + Kết quả trung gian trích xuất được: `role = "Trưởng phòng CNTT / IT Director"`.
+- **Bước 2 (Truy xuất Giới hạn số tiền dựa trên kết quả Bước 1)**:
+  + Query con 2: Tiêm trực tiếp kết quả của Bước 1 vào câu hỏi con thứ hai: `"Hạn mức số tiền tối đa được phê duyệt mua sắm của Trưởng phòng CNTT (IT Director) là bao nhiêu?"`
+  + Nguồn nhắm tới: Nguồn B (Bảng hạn mức phê duyệt tài chính theo vai trò).
+  + Kết quả trung gian trích xuất được: `limit = "500 triệu VNĐ"`.
+2. Tái hợp nhất câu trả lời (Recomposition &amp; Synthesis):
+- Tổng hợp hai bằng chứng đã trích xuất từ Nguồn A và B vào câu trả lời cuối cùng: 'Theo quy định mua sắm, Trưởng phòng CNTT là người có thẩm quyền phê duyệt việc mua phần mềm [Nguồn A], và hạn mức phê duyệt tối đa của vai trò này là 500 triệu VNĐ [Nguồn B].'
+3. Ràng buộc không dùng trí nhớ nội tại của model:
+- Nếu Bước 1 không tìm thấy vai trò hoặc Bước 2 không tìm thấy hạn mức từ nguồn tài liệu, hệ thống bắt buộc phải dừng và tuyên bố thiếu bằng chứng, tuyệt đối không cho phép LLM tự 'đoán' hạn mức dựa trên kiến thức thông thường ngoài đời.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Với các câu hỏi phức hợp đa chặng (Multi-hop Queries), việc truy xuất một lần (Single-step Retrieval) sẽ thất bại vì nguồn B không thể tìm kiếm chính xác nếu chưa biết vai trò trích xuất được từ nguồn A. Kỹ thuật Phân rã và Tái hợp nhất (Decompose-and-Recompose / Sub-question Querying) giúp kết nối thông tin giữa các tài liệu rời rạc một cách có căn cứ.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+LlamaIndex Documentation: 'Sub Question Query Engine' &amp; Press et al. (2022): 'Measuring and Reducing LLM Hallucination without Gold Answers'</t>
         </is>
       </c>
     </row>
@@ -794,10 +830,23 @@
       <c r="K7" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Kiểm tra lần lượt mức độ khái quát và khái niệm chi phối.
-Phân tích theo nguyên lý thiết kế: Kiểm tra lần lượt mức độ khái quát và khái niệm chi phối.</t>
+- [Chẩn đoán nguyên nhân thất bại] (1.0 điểm): Nhận diện lỗi từ vựng chi tiết (E419-X) không khớp với cách tổ chức phân cấp của tài liệu (Authentication/Session).
+- [Thiết kế Stepback Query chuẩn xác] (1.5 điểm): Đưa ra câu hỏi khái quát hóa đúng trọng tâm về cơ chế xác thực và hết hạn phiên.
+- [Biện minh không mở rộng thành mọi lỗi API] (1.5 điểm): Giải thích rõ việc mở rộng quá đà làm loãng ngữ nghĩa, tràn nhiễu và mất tính hữu dụng.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Phân tích nguyên nhân truy vấn trực tiếp thất bại:
+- Query trực tiếp `E419-X` thất bại vì tài liệu hướng dẫn không liệt kê mã lỗi chi tiết cấp thấp `E419-X` trong tiêu đề hoặc văn bản chính, mà tài liệu được tổ chức phân cấp theo các khái niệm trừu tượng cấp cao: nhóm Authentication (Xác thực) và Session Expiry (Hết hạn phiên làm việc).
+2. Thiết kế Stepback Query (Khái quát hóa có định hướng):
+- Nguyên lý Step-back Prompting: Lùi lại một bước để đặt câu hỏi về nguyên lý nền tảng hoặc khái niệm chi phối (Governing Principle), nhưng giữ nguyên ngữ cảnh ứng dụng thay vì biến thành câu hỏi chung chung vô nghĩa.
+- **Query Stepback được chọn**:
+  `"Cơ chế xử lý lỗi xác thực và chính sách hết hạn phiên làm việc (authentication and session expiry error handling)"`
+3. Biện minh vì sao không mở rộng thành 'mọi lỗi API':
+- Nếu mở rộng thành 'mọi lỗi API' (All API Errors): Ngữ nghĩa bị loãng hoàn toàn (Semantic Dilution), hệ thống sẽ truy xuất hàng trăm chunk về lỗi 400 Bad Request, 500 Server Error, Rate Limit... làm tràn ngập context bằng thông tin rác và đẩy phần kiến thức về session đi xa khỏi Top-K.
+- Query Stepback chọn lọc ở trên vừa đủ khái quát để khớp với nhóm tài liệu Authentication/Session Expiry, vừa đủ hẹp để giữ tỷ lệ tín hiệu trên nhiễu (Signal-to-Noise Ratio) ở mức cao nhất.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Kỹ thuật Step-back Querying giúp giải quyết khoảng cách từ vựng (Vocabulary Mismatch) khi người dùng hỏi các chi tiết quá cụ thể mà tài liệu chỉ giải thích ở cấp độ khái niệm chi phối. Sự cân bằng giữa mức độ khái quát (Generality) và sự tập trung chuyên đề (Specificity) là chìa khóa để retrieval thành công.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Zheng et al. (2023): 'Take a Step Back: Evoking Reasoning via Abstraction in Large Language Models' &amp; LangChain Step-Back Prompting</t>
         </is>
       </c>
     </row>
@@ -876,10 +925,24 @@
       <c r="K9" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Kiểm tra lần lượt tài liệu giả định và vector dạng câu trả lời.
-Phân tích theo nguyên lý thiết kế: Kiểm tra lần lượt tài liệu giả định và vector dạng câu trả lời.</t>
+- [Đánh giá đúng sai lầm chạy HyDE toàn bộ] (1.5 điểm): Phê phán có căn cứ: lãng phí độ trễ (500-1500ms), tốn chi phí LLM và nguy cơ hallucination làm lệch vector đúng.
+- [Xác định điều kiện kích hoạt có chọn lọc] (1.5 điểm): Đưa ra các trigger cụ thể: khoảng cách từ vựng lớn hoặc khi direct search trả điểm tin cậy thấp.
+- [Cơ chế Fallback an toàn] (1.0 điểm): Thiết lập cơ chế fallback về direct retrieval khi HyDE không cải thiện kết quả.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Đánh giá quyết định chạy HyDE cho mọi query (Evaluation of Universal HyDE):
+Quyết định này là **SAI LẦM VÀ LÃNG PHÍ KỸ THUẬT (Architectural Anti-Pattern)**:
+- Lãng phí độ trễ và chi phí: HyDE (Hypothetical Document Embeddings) đòi hỏi một lượt gọi LLM để sinh tài liệu giả định trước khi embed. Việc này làm tăng thêm từ 500 ms đến 1.500 ms độ trễ và tốn thêm token chi phí cho mỗi lượt tìm kiếm.
+- Rủi ro suy thoái chất lượng: Khi truy vấn trực tiếp đã xếp đúng nguồn ở vị trí 1 với độ trễ thấp, việc áp dụng HyDE có thể khiến tài liệu giả định sinh ra chứa các chi tiết ảo tưởng (hallucinated facts), làm lệch vector tìm kiếm ra khỏi nguồn đúng ban đầu.
+2. Điều kiện kích hoạt HyDE phù hợp (Gating / Trigger Conditions):
+Chỉ kích hoạt HyDE khi thỏa mãn một trong các điều kiện sau:
+- Điều kiện 1: Truy vấn có khoảng cách từ vựng lớn (High Vocabulary Mismatch) giữa câu hỏi và tài liệu trả lời (ví dụ: câu hỏi dạng tại sao/nguyên lý mà corpus chỉ chứa câu trả lời văn bản dài).
+- Điều kiện 2: Truy vấn trực tiếp trả về điểm tin cậy tương đồng vector quá thấp (`max_similarity_score &lt; threshold`, ví dụ &lt; 0.65).
+3. Phương án dự phòng và kiểm soát (Fallback Strategy):
+Nếu sau khi chạy HyDE mà kết quả tìm kiếm có điểm tương đồng thấp hơn hoặc phân tán hơn so với tìm kiếm trực tiếp, hệ thống lập tức fallback sử dụng danh sách kết quả của lượt tìm kiếm trực tiếp ban đầu.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+HyDE được thiết kế để giải quyết bài toán bất đối xứng ngữ nghĩa giữa câu hỏi ngắn và văn bản trả lời dài. Tuy nhiên, nó là một công cụ tốn kém về tài nguyên tính toán. Việc triển khai HyDE mù quáng cho 100% truy vấn vi phạm nguyên tắc thiết kế tiết kiệm (Lean Systems) và làm giảm SLO trải nghiệm người dùng.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Gao et al. (2022): 'Precise Zero-Shot Dense Retrieval without Relevance Labels' (HyDE Paper) &amp; LangChain HyDE Documentation</t>
         </is>
       </c>
     </row>
@@ -958,10 +1021,24 @@
       <c r="K11" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Kiểm tra lần lượt việc ánh xạ người dùng sang filter và Authorization trước khi tìm kiếm.
-Phân tích theo nguyên lý thiết kế: Kiểm tra lần lượt việc ánh xạ người dùng sang filter và Authorization trước khi tìm kiếm.</t>
+- [Phân biệt rạch ròi 2 trường hợp] (1.5 điểm): Phân biệt rõ kết quả rỗng do ràng buộc cấp quyền (chính sách hết hạn/mật) với lỗi thuật toán retrieval bỏ sót.
+- [Cấm gỡ bỏ bộ lọc quyền] (1.0 điểm): Khẳng định tuyệt đối không được bypass filter để tránh rò rỉ dữ liệu ngoài thẩm quyền.
+- [Cách xử lý &amp; Phản hồi minh bạch] (1.5 điểm): Thiết kế phản hồi an toàn cho người dùng thông báo không có chính sách hiệu lực và ghi log kiểm toán.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Phân biệt hai trường hợp bản chất khác nhau:
+- **Trường hợp A: Không có kết quả trong phạm vi được cấp quyền (Out-of-Scope / Authorization Constraint)**:
+  + Bản chất: Người dùng chỉ có quyền xem chính sách đang có hiệu lực (`is_active = true`). Bộ lọc quyền (RBAC / Tenant Scope Filter) hoạt động hoàn hảo và xác nhận rằng: Trong tập các tài liệu mà người dùng *được phép xem*, hoàn toàn không có tài liệu nào chứa nội dung câu hỏi.
+  + Việc tìm kiếm không dùng filter có nhiều kết quả tốt chứng minh các kết quả đó thuộc về chính sách đã hết hạn hoặc tài liệu nội bộ mật mà người dùng này *không có quyền truy cập*.
+- **Trường hợp B: Retrieval bỏ sót kết quả (Retrieval Recall Failure)**:
+  + Bản chất: Tài liệu đúng tồn tại trong tập người dùng được phép xem, nhưng thuật toán tìm kiếm vector/BM25 kém cỏi nên không tìm ra.
+2. Lựa chọn cách xử lý và phản hồi phù hợp:
+- Hành vi hệ thống: Tuyệt đối **KHÔNG ĐƯỢC** nới lỏng hoặc gỡ bỏ bộ lọc quyền để lấy kết quả ngoài phạm vi, vì đây là hành vi vi phạm nghiêm trọng an toàn thông tin (Authorization Bypass / Data Leakage Vulnerability).
+- Phản hồi chuẩn cho người dùng: Thông báo rõ ràng: 'Không tìm thấy chính sách có hiệu lực nào phù hợp với câu hỏi trong phạm vi quyền hạn của bạn. (Lưu ý: Một số tài liệu liên quan có thể thuộc phiên bản đã hết hiệu lực hoặc khu vực hạn chế)'.
+- Ghi nhật ký kiểm toán: Ghi log sự kiện truy vấn rỗng do bộ lọc quyền để đội ngũ quản trị nội dung xem xét cập nhật chính sách hiện hành nếu cần.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Bảo mật đa tầng trong RAG đòi hỏi việc thực thi quyền hạn (Access Scope Enforcement) phải là một ranh giới cứng (Hard Boundary). Không bao giờ được nhầm lẫn giữa sự vắng mặt của tài liệu được phép với lỗi truy xuất của thuật toán để rồi tự ý nới lỏng bảo mật.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+OWASP Top 10 for LLM: LLM06 Sensitive Information Disclosure &amp; Pinecone Multi-tenancy and Access Control</t>
         </is>
       </c>
     </row>
@@ -1044,10 +1121,27 @@
       <c r="K13" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: So sánh khả năng khớp ngữ nghĩa của dense với khả năng khớp lexical của sparse.
-Phân tích theo nguyên lý thiết kế: So sánh khả năng khớp ngữ nghĩa của dense với khả năng khớp lexical của sparse.</t>
+- [Phân tích đặc tính Dense vs BM25] (1.5 điểm): Chỉ ra Dense bắt được alias nhưng trượt part number; BM25 bắt part number nhưng trượt alias/typo.
+- [Thiết kế kiến trúc Hybrid với RRF] (1.5 điểm): Thiết kế pipeline chạy song song kết hợp RRF (hoặc weighted score) kèm tiền xử lý chính tả.
+- [Hệ thống metric kiểm chứng thực nghiệm] (1.0 điểm): Đưa ra phép đo Recall@5 và MRR phân tách trên 2 nhóm query để chứng minh ưu thế của Hybrid.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Phân tích ưu - nhược điểm đối lập của Dense và Sparse Retrieval:
+- Dense Retrieval (Vector Bi-Encoder): Rất mạnh về so khớp ngữ nghĩa và bắt được các từ đồng nghĩa/alias (ví dụ: 'máy tính xách tay' khớp với 'laptop'), nhưng rất kém khi khớp các mã định danh chính xác (Part Number, Serial, Error Code như `X-900`) vì các chuỗi ký tự này bị token hóa thành các subword rời rạc và bị phân tán trong không gian tiềm ẩn.
+- Sparse Retrieval (BM25 / Lexical): Rất mạnh về so khớp chính xác từng ký tự (Exact Keyword Match, Part Number), nhưng hoàn toàn thất bại khi gặp lỗi chính tả (typo) hoặc khi người dùng dùng từ đồng nghĩa/alias không trùng từ ngữ trong văn bản.
+2. Thiết kế Kiến trúc Hybrid Retrieval kết hợp Định tuyến (Hybrid Search Architecture):
+- **Thiết kế Pipeline Lai (Hybrid Search Pipeline)**:
+  + Chạy song song cả Dense Retriever và BM25 Retriever cho mọi truy vấn.
+  + Kết hợp kết quả bằng thuật toán Hợp nhất thứ hạng tương hỗ (Reciprocal Rank Fusion - RRF) với công thức: `RRF_Score(d) = 1/(60 + r_dense(d)) + 1/(60 + r_bm25(d))`.
+- **Bộ lọc tiền xử lý lỗi chính tả (Query Pre-processing Spellcheck)**: Tích hợp bộ sửa lỗi chính tả nhẹ (Spellchecker/SymSpell) trước khi đưa vào BM25 để giảm thiểu nhược điểm của lexical search.
+3. Hệ thống chỉ số kiểm chứng thực nghiệm (Evaluation Metrics):
+- Đo lường trên bộ kiểm thử 2 nhóm câu hỏi độc lập:
+  + Nhóm 1 (Alias &amp; Ngữ nghĩa): Đo Recall@5 và MRR (yêu cầu Hybrid đạt kết quả tương đương Dense).
+  + Nhóm 2 (Part Number &amp; Mã lỗi): Đo Recall@5 và Precision@1 (yêu cầu Hybrid đạt kết quả tương đương BM25).
+- Mục tiêu nghiệm thu: Hybrid Search đạt Recall@5 toàn cục cao hơn ít nhất 10% so với việc chỉ dùng riêng lẻ Dense hoặc BM25.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Dense Retrieval và Sparse Retrieval bổ trợ hoàn hảo cho nhau: Dense giải quyết sự bất đối xứng từ vựng và đồng nghĩa, còn Sparse giải quyết tính chính xác tuyệt đối của mã định danh và thuật ngữ hiếm. Kết hợp hai phương pháp bằng RRF là tiêu chuẩn vàng của hệ thống RAG hiện đại.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Cormack, Clarke &amp; Büttcher (2009): 'Reciprocal Rank Fusion outperforms Condorcet and individual machine learning methods' &amp; Pinecone Hybrid Search</t>
         </is>
       </c>
     </row>
@@ -1178,10 +1272,25 @@
       <c r="K16" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Xác nhận điểm đã được chuẩn hóa rồi so sánh nhiều giá trị alpha.
-Phân tích theo nguyên lý thiết kế: Xác nhận điểm đã được chuẩn hóa rồi so sánh nhiều giá trị alpha.</t>
+- [Quyết định tạm hoãn có căn cứ] (1.5 điểm): Tạm hoãn chọn alpha=0.5 vì làm giảm mạnh chất lượng ở nhóm policy tiếng Việt, không để điểm trung bình che giấu lỗi.
+- [Báo cáo mức suy thoái minh bạch] (1.0 điểm): Yêu cầu báo cáo số liệu giảm chất lượng cụ thể của nhóm tiếng Việt và nhóm ID chính xác.
+- [Đề xuất Dynamic Alpha hoặc RRF] (1.5 điểm): Đưa ra giải pháp kỹ thuật: định tuyến alpha động theo loại câu hỏi hoặc thay thế bằng RRF phi tham số.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Quyết định: **TẠM HOÃN CHỌN ALPHA TOÀN CỤC (POSTPONE GLOBAL ALPHA SELECTION)**:
+Căn cứ: Mặc dù `alpha = 0,5` có điểm trung bình tổng thể cao nhất, nhưng nó lại gây ra hiện tượng sụt giảm nghiêm trọng (Severe Performance Degradation) ở nhóm chính sách tiếng Việt. Việc hy sinh chất lượng của một phân khúc người dùng quan trọng để đổi lấy con số trung bình đẹp là một quyết định kỹ thuật thiên lệch và nguy hiểm.
+2. Báo cáo mức giảm chất lượng cần công bố minh bạch (Degradation Reporting):
+- Báo cáo rõ ràng mức sụt giảm cụ thể của từng nhóm truy vấn so với cấu hình tốt nhất của nhóm đó:
+  + Nhóm truy vấn chính sách tiếng Việt: Báo cáo mức giảm Recall@5 và MRR khi chuyển từ alpha tối ưu của tiếng Việt (ví dụ `alpha = 0,8`) sang `alpha = 0,5` (mức giảm cụ thể, ví dụ giảm 18% Recall).
+  + Nhóm truy vấn ID chính xác: Báo cáo mức giảm khi chuyển từ `alpha = 0,2` sang `0,5`.
+3. Đề xuất giải pháp kỹ thuật vượt qua bế tắc:
+- Chuyển từ Alpha Tĩnh toàn cục (Static Global Alpha) sang **Alpha Động theo phân loại truy vấn (Dynamic / Query-Class-Dependent Alpha)**:
+  + Nếu bộ phân loại phát hiện query là mã ID / Part Number / Ký tự đặc biệt: Tự động gán `alpha = 0,2` (ưu tiên BM25).
+  + Nếu query là câu hỏi ngữ nghĩa tiếng Việt: Tự động gán `alpha = 0,8` (ưu tiên Dense).
+  + Hoặc chuyển đổi hoàn toàn sang phương pháp dung hợp phi tham số không phụ thuộc alpha: **Reciprocal Rank Fusion (RRF)**.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Hiện tượng nghịch lý trung bình (Flaw of Averages) trong tinh chỉnh siêu tham số RAG: một giá trị trung bình có thể che giấu sự sụp đổ chất lượng ở một nhóm ngôn ngữ hoặc nhóm tác vụ đặc thù. Kỹ sư hệ thống phải báo cáo minh bạch mức suy thoái theo từng cohort và chuyển dịch sang cơ chế thích ứng động (Dynamic Alpha) hoặc RRF.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Pinecone Documentation: 'Tuning Alpha for Hybrid Search' &amp; Kohavi: 'Controlled Experiments and Subgroup Analysis'</t>
         </is>
       </c>
     </row>
@@ -1212,10 +1321,25 @@
       <c r="K17" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Xác nhận điểm đã được chuẩn hóa rồi so sánh nhiều giá trị alpha.
-Phân tích theo nguyên lý thiết kế: Xác nhận điểm đã được chuẩn hóa rồi so sánh nhiều giá trị alpha.</t>
+- [Thiết kế phép quét Alpha đa điểm] (1.5 điểm): Thiết lập lưới quét alpha từ 0.0 đến 1.0 bước 0.1 trên tập benchmark đóng băng với điểm đã chuẩn hóa.
+- [Cấu trúc bản ghi quyết định ADR] (1.5 điểm): Soạn thảo cấu trúc ADR đầy đủ: Bối cảnh, Dữ liệu thực nghiệm, Quyết định, Đánh đổi và Điều kiện xem lại.
+- [Phê phán việc lấy số từ slide] (1.0 điểm): Nhấn mạnh nguyên tắc cấm áp đặt giá trị alpha lý thuyết lên corpus mới mà không đo lường.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Thiết kế phép thử quét nhiều giá trị Alpha (Multi-Alpha Parameter Sweep):
+- Cố định tập ngữ liệu và bộ testset chuẩn hóa đã được đánh nhãn (Frozen Evaluation Benchmark).
+- Đảm bảo điểm số từ Dense và BM25 đã được chuẩn hóa đúng (Min-Max Scaling hoặc Standard Z-Score) về cùng khoảng giá trị `[0, 1]`.
+- Thiết lập lưới quét giá trị `alpha` từ 0.0 đến 1.0 với bước nhảy 0.1: `alpha in [0.0, 0.1, 0.2, 0.3, 0.4, 0.5, 0.6, 0.7, 0.8, 0.9, 1.0]` (trong đó 0.0 là thuần BM25, 1.0 là thuần Dense).
+- Đo lường các chỉ số cốt lõi tại mỗi điểm: Recall@5, Precision@5, MRR và NDCG@5 trên cả tập tổng thể và từng nhóm câu hỏi (keyword vs semantic).
+2. Nội dung cần ghi trong Bản ghi Quyết định Kỹ thuật (Architecture Decision Record - ADR):
+Tạo tài liệu `ADR-042: Lựa chọn Tham số Alpha cho Hybrid Search Corpus Mới` bao gồm:
+- **Bối cảnh &amp; Dữ liệu thực nghiệm**: Mô tả đặc tính của corpus mới và biểu đồ hiệu năng Recall/MRR theo từng giá trị alpha được quét thực tế.
+- **Quyết định (Decision)**: Giá trị alpha được lựa chọn (kèm lý do tại sao không áp dụng con số 0.7 từ slide lý thuyết cũ).
+- **Hậu quả &amp; Đánh đổi (Trade-offs)**: Phân tích nhóm truy vấn nào hưởng lợi nhiều nhất và nhóm nào có thể bị ảnh hưởng nhẹ.
+- **Điều kiện tái đánh giá**: Quy định khi nào cần tinh chỉnh lại alpha (ví dụ: khi kích thước corpus tăng gấp đôi hoặc khi thay đổi mô hình embedding mới).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Không bao giờ được sao chép máy móc các siêu tham số từ slide lý thuyết sang một tập ngữ liệu thực tế mới mà không qua thực nghiệm chuẩn hóa. Mỗi corpus có phân phối từ vựng và đặc trưng ngữ nghĩa riêng biệt. Quy trình Architecture Decision Record (ADR) bảo đảm mọi quyết định cấu hình hệ thống đều dựa trên bằng chứng dữ liệu có thể kiểm chứng.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Michael Nygard: 'Documenting Architecture Decisions' (ADR Template) &amp; Qdrant Hybrid Search Tuning Guide</t>
         </is>
       </c>
     </row>
@@ -1294,10 +1418,20 @@
       <c r="K19" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Xem xét tần suất từ và nghịch đảo tần suất tài liệu.
-Phân tích theo nguyên lý thiết kế: Xem xét tần suất từ và nghịch đảo tần suất tài liệu.</t>
+- [Giải thích vai trò của IDF] (1.5 điểm): Nêu rõ từ hiếm có IDF cao, đóng vai trò tín hiệu phân biệt mạnh mẽ giúp tăng vọt điểm số BM25.
+- [Giải thích chuẩn hóa độ dài tài liệu] (1.5 điểm): Phân tích cơ chế phạt tài liệu dài và ưu tiên tài liệu ngắn có mật độ thông tin tập trung.
+- [Kết luận so sánh giữa C và D] (1.0 điểm): Khẳng định Tài liệu C đạt điểm cao hơn D do độ dài ngắn hơn mà không cần tính toán số học cụ thể.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Vai trò của IDF (Inverse Document Frequency - Nghịch đảo tần suất tài liệu):
+- Ý nghĩa: IDF đo lường mức độ quan trọng và độ hiếm của một từ khóa trong toàn bộ kho tài liệu (Corpus). Một từ xuất hiện ở hầu hết mọi tài liệu (như từ nối, từ dừng) sẽ có IDF xấp xỉ 0, không có giá trị phân biệt.
+- Ứng dụng trong bối cảnh: Vì từ trong câu hỏi là 'rất hiếm trong corpus', giá trị IDF của nó cực kỳ cao. Khi xuất hiện trong tài liệu, nó đóng vai trò là một tín hiệu định danh mạnh mẽ (Strong Discriminative Signal), giúp nâng điểm số BM25 của tài liệu lên rất cao so với các tài liệu không chứa từ này.
+2. Vai trò của việc Chuẩn hóa độ dài tài liệu (Document Length Normalization - Tham số b trong BM25):
+- Ý nghĩa: Thuật toán BM25 áp dụng cơ chế phạt các tài liệu có độ dài lớn thông qua tỷ lệ độ dài tài liệu so với độ dài trung bình toàn kho (`len(doc) / avg_len`). Một tài liệu dài chứa từ khóa nhiều khả năng là do ngẫu nhiên thống kê, trong khi tài liệu ngắn chứa từ khóa chứng tỏ mật độ thông tin và độ tập trung chủ đề rất cao.
+- So sánh giữa Tài liệu C và D: Cả C và D đều có cùng số lần xuất hiện của từ khóa hiếm, nhưng Tài liệu C ngắn hơn nhiều so với Tài liệu D. Cơ chế chuẩn hóa độ dài của BM25 sẽ ưu tiên mạnh cho Tài liệu C, giúp C đạt điểm BM25 cao hơn đáng kể so với D vì mật độ từ khóa (Term Density) của C vượt trội và không bị pha loãng bởi các nội dung râu ria.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+BM25 là thuật toán xếp hạng xác suất dựa trên hai trụ cột: Tần suất từ có bão hòa (Saturated TF kết hợp với Length Normalization qua tham số b) và Mức độ phân biệt thông tin toàn cục (IDF). Việc hiểu rõ vai trò của việc chuẩn hóa độ dài giúp giải thích tại sao các đoạn trích ngắn, cô đọng lại được xếp hạng cao hơn các văn bản dài dòng chứa cùng số lần xuất hiện từ khóa.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Robertson &amp; Zaragoza (2009): 'The Probabilistic Relevance Framework: BM25 and Beyond' (Foundations and Trends in Information Retrieval)</t>
         </is>
       </c>
     </row>
@@ -1380,10 +1514,22 @@
       <c r="K21" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Kiểm tra quy ước tokenization và cách xây dựng index.
-Phân tích theo nguyên lý thiết kế: Kiểm tra quy ước tokenization và cách xây dựng index.</t>
+- [Chỉ rõ lỗi mất Record ID] (1.5 điểm): Nhận diện lỗi BM25 làm mất ID khiến bước gộp hybrid coi là bản ghi mới và gây duplicate.
+- [Chỉ rõ lỗi vi phạm Top-K] (1.0 điểm): Nhận diện lỗi yêu cầu top_k=2 nhưng trả về 5 bản ghi do thiếu bước slice/truncate kết quả.
+- [Bổ sung 2 Assertion Invariants cụ thể] (1.5 điểm): Viết rõ 2 điều kiện kiểm tra: bắt buộc có record_id không rỗng và độ dài danh sách &lt;= top_k.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Chỉ ra hai lỗi nghiêm trọng trong quá trình thực thi (Defect Identification):
+- **Lỗi 1: Thất thoát Khóa định danh bản ghi (Missing Record ID in Search Output)**:
+  + Chi tiết: Bước tìm kiếm BM25 trả về văn bản nhưng làm rơi mất trường `record_id` (hoặc trả về `id: null`). Hậu quả là bước gộp Hybrid Search không thể đối soát và so khớp bản ghi này với bản ghi trả về từ Dense Search. Thuật toán gộp buộc phải coi đây là một bản ghi hoàn toàn mới, gây ra hiện tượng nhân bản kết quả (Duplicate Result Pollution) và làm sai lệch thuật toán RRF/Score Fusion.
+- **Lỗi 2: Vi phạm Hợp đồng Giới hạn kích thước đầu ra (Top-K Limit Violation)**:
+  + Chi tiết: Lệnh gọi API yêu cầu rõ ràng `top_k = 2`, nhưng hệ thống lại trả về tới 5 bản ghi. Điều này vi phạm nghiêm trọng hợp đồng API tìm kiếm, chứng minh thuật toán ranking đã quên bước cắt lát kết quả (`return results[:k]`).
+2. Các điều kiện kiểm tra (Assertion Invariants) cần bổ sung vào hệ thống:
+- Invariant 1 (Strict Schema &amp; ID Presence): `assert all(r.get('record_id') is not None and len(r['record_id']) &gt; 0 for r in search_results)` — Mọi kết quả trả về từ BM25 bắt buộc phải mang ID bản ghi hợp lệ.
+- Invariant 2 (Strict Top-K Contract): `assert len(search_results) &lt;= top_k` — Số lượng kết quả trả về không bao giờ được vượt quá giá trị `top_k` yêu cầu.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong kiến trúc tìm kiếm phân tán, mọi Retriever (dù là Dense hay BM25) đều phải tuân thủ nghiêm ngặt Giao ước Dữ liệu (Component Contract): bảo toàn khóa định danh duy nhất để phục vụ deduplication và tôn trọng ngưỡng giới hạn Top-K. Vi phạm giao ước này sẽ phá hủy tính toàn vẹn của tầng Fusion phía sau.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Elasticsearch / Lucene Documentation: 'TopDocs, ScoredDoc and API Contract Guidelines'</t>
         </is>
       </c>
     </row>
